--- a/漳州菜篮子_零售价格日报表.xlsx
+++ b/漳州菜篮子_零售价格日报表.xlsx
@@ -16,6 +16,7 @@
     <sheet name="06-24" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="06-23" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="06-22" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="06-21" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -86,6 +87,60 @@
       <b val="1"/>
       <color rgb="002E7D32"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="002E7D32"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00999999"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00008000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00999999"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="5">
@@ -160,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -215,6 +270,56 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2928,6 +3033,1548 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>漳州菜篮子 — 零售价格日报表</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>日期：2026年06月21日（星期日） | 单位：元/500g | 数据来源：漳州菜篮子网</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>品名</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>平均价（元/500g）</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>较上日涨跌幅</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>📂 水果（9 个品种）</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+      <c r="E4" s="19" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>水果</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>富士苹果</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="D5" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>水果</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>鸭梨</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E6" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>水果</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>西瓜</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="34" t="inlineStr">
+        <is>
+          <t>↓ -2.44%</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>水果</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>进口莲雾</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="D8" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>水果</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>山竹</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="D9" s="34" t="inlineStr">
+        <is>
+          <t>↓ -2.27%</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>水果</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>火龙果（白肉）</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="D10" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E10" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>水果</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>本地香蕉</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D11" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>水果</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>本地菠萝</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="35" t="inlineStr">
+        <is>
+          <t>↑ +1.69%</t>
+        </is>
+      </c>
+      <c r="E12" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>水果</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>荔枝（乌叶）</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="D13" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>📂 肉禽蛋（10 个品种）</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="19" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>肉禽蛋</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>猪瘦肉</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="D15" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>肉禽蛋</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="inlineStr">
+        <is>
+          <t>五花肉</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n">
+        <v>13</v>
+      </c>
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E16" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>肉禽蛋</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>带皮后腿肉</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="30" t="inlineStr">
+        <is>
+          <t>肉禽蛋</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>排骨</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="D18" s="36" t="inlineStr">
+        <is>
+          <t>↓ -0.79%</t>
+        </is>
+      </c>
+      <c r="E18" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>肉禽蛋</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>牛腱子肉</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="n">
+        <v>45</v>
+      </c>
+      <c r="D19" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>肉禽蛋</t>
+        </is>
+      </c>
+      <c r="B20" s="31" t="inlineStr">
+        <is>
+          <t>牛腩</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="n">
+        <v>42</v>
+      </c>
+      <c r="D20" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E20" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>肉禽蛋</t>
+        </is>
+      </c>
+      <c r="B21" s="27" t="inlineStr">
+        <is>
+          <t>白条鸡</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D21" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E21" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>肉禽蛋</t>
+        </is>
+      </c>
+      <c r="B22" s="31" t="inlineStr">
+        <is>
+          <t>白条鸭（菜鸭）</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="D22" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E22" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>肉禽蛋</t>
+        </is>
+      </c>
+      <c r="B23" s="27" t="inlineStr">
+        <is>
+          <t>鸡场蛋</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D23" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E23" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>肉禽蛋</t>
+        </is>
+      </c>
+      <c r="B24" s="31" t="inlineStr">
+        <is>
+          <t>鸭蛋</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D24" s="35" t="inlineStr">
+        <is>
+          <t>↑ +1.56%</t>
+        </is>
+      </c>
+      <c r="E24" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>📂 水产（6 个品种）</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="n"/>
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="19" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>水产</t>
+        </is>
+      </c>
+      <c r="B26" s="31" t="inlineStr">
+        <is>
+          <t>冻带鱼（250g）</t>
+        </is>
+      </c>
+      <c r="C26" s="32" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D26" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E26" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>水产</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="inlineStr">
+        <is>
+          <t>草鱼（1000g）</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D27" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>水产</t>
+        </is>
+      </c>
+      <c r="B28" s="31" t="inlineStr">
+        <is>
+          <t>冻黄鱼（500g）</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n">
+        <v>26</v>
+      </c>
+      <c r="D28" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E28" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>水产</t>
+        </is>
+      </c>
+      <c r="B29" s="27" t="inlineStr">
+        <is>
+          <t>鳙鱼（1500g）</t>
+        </is>
+      </c>
+      <c r="C29" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="D29" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E29" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>水产</t>
+        </is>
+      </c>
+      <c r="B30" s="31" t="inlineStr">
+        <is>
+          <t>白鲫鱼（350g）</t>
+        </is>
+      </c>
+      <c r="C30" s="32" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="D30" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E30" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t>水产</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="inlineStr">
+        <is>
+          <t>活虾（10cm）</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="D31" s="37" t="inlineStr">
+        <is>
+          <t>↑ +0.70%</t>
+        </is>
+      </c>
+      <c r="E31" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>📂 粮油（24 个品种）</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="n"/>
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="19" t="n"/>
+      <c r="E32" s="19" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="inlineStr">
+        <is>
+          <t>黄豆</t>
+        </is>
+      </c>
+      <c r="C33" s="28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D33" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E33" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B34" s="31" t="inlineStr">
+        <is>
+          <t>绿豆</t>
+        </is>
+      </c>
+      <c r="C34" s="32" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="D34" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E34" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="26" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="inlineStr">
+        <is>
+          <t>晚籼米（煮干饭）</t>
+        </is>
+      </c>
+      <c r="C35" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E35" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B36" s="31" t="inlineStr">
+        <is>
+          <t>粳米（珍珠米煮稀饭）</t>
+        </is>
+      </c>
+      <c r="C36" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E36" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="26" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="inlineStr">
+        <is>
+          <t>东北米（珍珠米）5公斤小包装</t>
+        </is>
+      </c>
+      <c r="C37" s="28" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="D37" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E37" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="30" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B38" s="31" t="inlineStr">
+        <is>
+          <t>面粉（标准粉）</t>
+        </is>
+      </c>
+      <c r="C38" s="32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D38" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E38" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="inlineStr">
+        <is>
+          <t>菜籽油（5L/桶）金龙鱼</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="n">
+        <v>70</v>
+      </c>
+      <c r="D39" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E39" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="30" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B40" s="31" t="inlineStr">
+        <is>
+          <t>大豆油（5L/桶）金龙鱼</t>
+        </is>
+      </c>
+      <c r="C40" s="32" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="D40" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E40" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="26" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="inlineStr">
+        <is>
+          <t>花生油（5L/桶）金龙鱼</t>
+        </is>
+      </c>
+      <c r="C41" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="D41" s="34" t="inlineStr">
+        <is>
+          <t>↓ -1.64%</t>
+        </is>
+      </c>
+      <c r="E41" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="30" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B42" s="31" t="inlineStr">
+        <is>
+          <t>第二代食用调和油（5L/桶）金龙鱼</t>
+        </is>
+      </c>
+      <c r="C42" s="32" t="n">
+        <v>65</v>
+      </c>
+      <c r="D42" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E42" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="inlineStr">
+        <is>
+          <t>鲁花花生油（5L/桶）</t>
+        </is>
+      </c>
+      <c r="C43" s="28" t="n">
+        <v>150</v>
+      </c>
+      <c r="D43" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E43" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="30" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B44" s="31" t="inlineStr">
+        <is>
+          <t>金鼠香米（斤）</t>
+        </is>
+      </c>
+      <c r="C44" s="32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D44" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E44" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B45" s="27" t="inlineStr">
+        <is>
+          <t>广洋湖香粘米（斤）</t>
+        </is>
+      </c>
+      <c r="C45" s="28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D45" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E45" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="30" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B46" s="31" t="inlineStr">
+        <is>
+          <t>盘锦大米（斤）</t>
+        </is>
+      </c>
+      <c r="C46" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D46" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E46" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="inlineStr">
+        <is>
+          <t>洪家鸡油粘香米（5KG/包）</t>
+        </is>
+      </c>
+      <c r="C47" s="28" t="n">
+        <v>39</v>
+      </c>
+      <c r="D47" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E47" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="30" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B48" s="31" t="inlineStr">
+        <is>
+          <t>十月稻田长粒香米（5KG/包）</t>
+        </is>
+      </c>
+      <c r="C48" s="32" t="n">
+        <v>70</v>
+      </c>
+      <c r="D48" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E48" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="26" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
+        <is>
+          <t>十月稻田香稻贡米（5KG/包）</t>
+        </is>
+      </c>
+      <c r="C49" s="28" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="D49" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E49" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="30" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B50" s="31" t="inlineStr">
+        <is>
+          <t>小悦米（5KG/包）</t>
+        </is>
+      </c>
+      <c r="C50" s="32" t="n">
+        <v>48</v>
+      </c>
+      <c r="D50" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E50" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>九三非转基因大豆油（10L/桶）</t>
+        </is>
+      </c>
+      <c r="C51" s="28" t="n">
+        <v>160</v>
+      </c>
+      <c r="D51" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E51" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="30" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B52" s="31" t="inlineStr">
+        <is>
+          <t>九三压榨浓香花生油（5L/桶）</t>
+        </is>
+      </c>
+      <c r="C52" s="32" t="n">
+        <v>158</v>
+      </c>
+      <c r="D52" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E52" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="26" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B53" s="27" t="inlineStr">
+        <is>
+          <t>馒头粉（斤）</t>
+        </is>
+      </c>
+      <c r="C53" s="28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D53" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E53" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="30" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B54" s="31" t="inlineStr">
+        <is>
+          <t>玉米淀粉（斤）</t>
+        </is>
+      </c>
+      <c r="C54" s="32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D54" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E54" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="26" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B55" s="27" t="inlineStr">
+        <is>
+          <t>大树碱面（1500g/件）</t>
+        </is>
+      </c>
+      <c r="C55" s="28" t="n">
+        <v>41</v>
+      </c>
+      <c r="D55" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E55" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="30" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B56" s="31" t="inlineStr">
+        <is>
+          <t>糯米</t>
+        </is>
+      </c>
+      <c r="C56" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D56" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E56" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="25" t="inlineStr">
+        <is>
+          <t>📂 其它（7 个品种）</t>
+        </is>
+      </c>
+      <c r="B57" s="19" t="n"/>
+      <c r="C57" s="19" t="n"/>
+      <c r="D57" s="19" t="n"/>
+      <c r="E57" s="19" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="30" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="B58" s="31" t="inlineStr">
+        <is>
+          <t>香菇</t>
+        </is>
+      </c>
+      <c r="C58" s="32" t="n">
+        <v>50</v>
+      </c>
+      <c r="D58" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E58" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="26" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="B59" s="27" t="inlineStr">
+        <is>
+          <t>水豆腐（块）</t>
+        </is>
+      </c>
+      <c r="C59" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E59" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="30" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="B60" s="31" t="inlineStr">
+        <is>
+          <t>晶华自然盐（400g/袋）</t>
+        </is>
+      </c>
+      <c r="C60" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E60" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="26" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="B61" s="27" t="inlineStr">
+        <is>
+          <t>冰度白砂糖（400g/袋）</t>
+        </is>
+      </c>
+      <c r="C61" s="28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D61" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E61" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="30" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="B62" s="31" t="inlineStr">
+        <is>
+          <t>冰度红糖（400g/袋）</t>
+        </is>
+      </c>
+      <c r="C62" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D62" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E62" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="26" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="B63" s="27" t="inlineStr">
+        <is>
+          <t>恒顺陈醋（500ml/瓶）</t>
+        </is>
+      </c>
+      <c r="C63" s="28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D63" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E63" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="30" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="B64" s="31" t="inlineStr">
+        <is>
+          <t>蜜蜂味精（454g/袋）</t>
+        </is>
+      </c>
+      <c r="C64" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="D64" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E64" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="38" t="inlineStr">
+        <is>
+          <t>📊 共 56 个品种 | 上涨 3 | 下跌 4 | 持平 49 | 无对比 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="39" t="inlineStr">
+        <is>
+          <t>↑ 红色=涨  ↓ 绿色=跌  → 灰色=持平  — =无上日数据</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A66:E66"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -19469,10 +21116,10 @@
           <t>📂 蔬菜（32 个品种）</t>
         </is>
       </c>
-      <c r="B4" s="19" t="n"/>
-      <c r="C4" s="19" t="n"/>
-      <c r="D4" s="19" t="n"/>
-      <c r="E4" s="19" t="n"/>
+      <c r="B4" s="20" t="n"/>
+      <c r="C4" s="20" t="n"/>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="21" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -20280,10 +21927,10 @@
           <t>📂 水果（9 个品种）</t>
         </is>
       </c>
-      <c r="B37" s="19" t="n"/>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="19" t="n"/>
-      <c r="E37" s="19" t="n"/>
+      <c r="B37" s="20" t="n"/>
+      <c r="C37" s="20" t="n"/>
+      <c r="D37" s="20" t="n"/>
+      <c r="E37" s="21" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -20516,10 +22163,10 @@
           <t>📂 肉禽蛋（10 个品种）</t>
         </is>
       </c>
-      <c r="B47" s="19" t="n"/>
-      <c r="C47" s="19" t="n"/>
-      <c r="D47" s="19" t="n"/>
-      <c r="E47" s="19" t="n"/>
+      <c r="B47" s="20" t="n"/>
+      <c r="C47" s="20" t="n"/>
+      <c r="D47" s="20" t="n"/>
+      <c r="E47" s="21" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -20777,10 +22424,10 @@
           <t>📂 水产（6 个品种）</t>
         </is>
       </c>
-      <c r="B58" s="19" t="n"/>
-      <c r="C58" s="19" t="n"/>
-      <c r="D58" s="19" t="n"/>
-      <c r="E58" s="19" t="n"/>
+      <c r="B58" s="20" t="n"/>
+      <c r="C58" s="20" t="n"/>
+      <c r="D58" s="20" t="n"/>
+      <c r="E58" s="21" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
@@ -20938,10 +22585,10 @@
           <t>📂 粮油（24 个品种）</t>
         </is>
       </c>
-      <c r="B65" s="19" t="n"/>
-      <c r="C65" s="19" t="n"/>
-      <c r="D65" s="19" t="n"/>
-      <c r="E65" s="19" t="n"/>
+      <c r="B65" s="20" t="n"/>
+      <c r="C65" s="20" t="n"/>
+      <c r="D65" s="20" t="n"/>
+      <c r="E65" s="21" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -21549,10 +23196,10 @@
           <t>📂 其它（7 个品种）</t>
         </is>
       </c>
-      <c r="B90" s="19" t="n"/>
-      <c r="C90" s="19" t="n"/>
-      <c r="D90" s="19" t="n"/>
-      <c r="E90" s="19" t="n"/>
+      <c r="B90" s="20" t="n"/>
+      <c r="C90" s="20" t="n"/>
+      <c r="D90" s="20" t="n"/>
+      <c r="E90" s="21" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">

--- a/漳州菜篮子_零售价格日报表.xlsx
+++ b/漳州菜篮子_零售价格日报表.xlsx
@@ -122,13 +122,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00FF0000"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FF0000"/>
+      <color rgb="00008000"/>
       <sz val="11"/>
     </font>
     <font>
@@ -306,13 +306,13 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -696,48 +696,48 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>漳州菜篮子 — 零售价格日报表</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>日期：2026年06月30日（星期二） | 单位：元/500g | 数据来源：漳州菜篮子网</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>分类</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>品名</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>平均价（元/500g）</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="24" t="inlineStr">
         <is>
           <t>较上日涨跌幅</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>📂 蔬菜（32 个品种）</t>
         </is>
@@ -748,807 +748,807 @@
       <c r="E4" s="21" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>老姜</t>
         </is>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="28" t="n">
         <v>7.9</v>
       </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>蒜头</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>葱</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="28" t="n">
         <v>6.3</v>
       </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>芹菜</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="32" t="n">
         <v>6.9</v>
       </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="D8" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>大白菜</t>
         </is>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="28" t="n">
         <v>2.5</v>
       </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>上海青</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="32" t="n">
         <v>4.4</v>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="34" t="inlineStr">
         <is>
           <t>↑ +2.33%</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>黄瓜</t>
         </is>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="28" t="n">
         <v>3.1</v>
       </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>白萝卜</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="32" t="n">
         <v>2.5</v>
       </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>长茄</t>
         </is>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="28" t="n">
         <v>4.8</v>
       </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>西红柿</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="32" t="n">
         <v>4.5</v>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="35" t="inlineStr">
         <is>
           <t>↓ -2.17%</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>土豆</t>
         </is>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C15" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>胡萝卜</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E16" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>青椒</t>
         </is>
       </c>
-      <c r="C17" s="10" t="n">
+      <c r="C17" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="A18" s="30" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>尖椒</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C18" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E18" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
         <is>
           <t>包菜</t>
         </is>
       </c>
-      <c r="C19" s="10" t="n">
+      <c r="C19" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>蒜苔</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C20" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E20" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B21" s="27" t="inlineStr">
         <is>
           <t>花菜</t>
         </is>
       </c>
-      <c r="C21" s="10" t="n">
+      <c r="C21" s="28" t="n">
         <v>4.8</v>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="36" t="inlineStr">
         <is>
           <t>↑ +2.13%</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B22" s="31" t="inlineStr">
         <is>
           <t>韭菜</t>
         </is>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="C22" s="32" t="n">
         <v>4.6</v>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D22" s="34" t="inlineStr">
         <is>
           <t>↑ +2.22%</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B23" s="27" t="inlineStr">
         <is>
           <t>空心菜</t>
         </is>
       </c>
-      <c r="C23" s="10" t="n">
+      <c r="C23" s="28" t="n">
         <v>4.7</v>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="36" t="inlineStr">
         <is>
           <t>↑ +4.44%</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B24" s="31" t="inlineStr">
         <is>
           <t>绿豆芽</t>
         </is>
       </c>
-      <c r="C24" s="6" t="n">
+      <c r="C24" s="32" t="n">
         <v>2.1</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="D24" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E24" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B25" s="27" t="inlineStr">
         <is>
           <t>油菜</t>
         </is>
       </c>
-      <c r="C25" s="10" t="n">
+      <c r="C25" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="36" t="inlineStr">
         <is>
           <t>↑ +11.11%</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>油麦菜</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n">
+      <c r="C26" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="D26" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E26" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="inlineStr">
         <is>
           <t>菠菜</t>
         </is>
       </c>
-      <c r="C27" s="10" t="n">
+      <c r="C27" s="28" t="n">
         <v>6.9</v>
       </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="D27" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E27" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B28" s="31" t="inlineStr">
         <is>
           <t>生菜</t>
         </is>
       </c>
-      <c r="C28" s="6" t="n">
+      <c r="C28" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="D28" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E28" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B29" s="27" t="inlineStr">
         <is>
           <t>苋菜（红）</t>
         </is>
       </c>
-      <c r="C29" s="10" t="n">
+      <c r="C29" s="28" t="n">
         <v>5.4</v>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D29" s="36" t="inlineStr">
         <is>
           <t>↑ +10.20%</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B30" s="31" t="inlineStr">
         <is>
           <t>地瓜叶</t>
         </is>
       </c>
-      <c r="C30" s="6" t="n">
+      <c r="C30" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="D30" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E30" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="inlineStr">
         <is>
           <t>西芹</t>
         </is>
       </c>
-      <c r="C31" s="10" t="n">
+      <c r="C31" s="28" t="n">
         <v>4.7</v>
       </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="D31" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E31" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B32" s="31" t="inlineStr">
         <is>
           <t>西兰花</t>
         </is>
       </c>
-      <c r="C32" s="6" t="n">
+      <c r="C32" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="D32" s="14" t="inlineStr">
+      <c r="D32" s="34" t="inlineStr">
         <is>
           <t>↑ +1.69%</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E32" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="inlineStr">
         <is>
           <t>本地芥菜</t>
         </is>
       </c>
-      <c r="C33" s="10" t="n">
+      <c r="C33" s="28" t="n">
         <v>4.25</v>
       </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="D33" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E33" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B34" s="31" t="inlineStr">
         <is>
           <t>莴笋</t>
         </is>
       </c>
-      <c r="C34" s="6" t="n">
+      <c r="C34" s="32" t="n">
         <v>3.7</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="D34" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E34" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="A35" s="26" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="inlineStr">
         <is>
           <t>冬瓜</t>
         </is>
       </c>
-      <c r="C35" s="10" t="n">
+      <c r="C35" s="28" t="n">
         <v>2.1</v>
       </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="D35" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E35" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B36" s="31" t="inlineStr">
         <is>
           <t>角瓜</t>
         </is>
       </c>
-      <c r="C36" s="6" t="n">
+      <c r="C36" s="32" t="n">
         <v>5.6</v>
       </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="D36" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E36" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="25" t="inlineStr">
         <is>
           <t>📂 水果（9 个品种）</t>
         </is>
@@ -1559,232 +1559,232 @@
       <c r="E37" s="21" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="30" t="inlineStr">
         <is>
           <t>水果</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="31" t="inlineStr">
         <is>
           <t>富士苹果</t>
         </is>
       </c>
-      <c r="C38" s="6" t="n">
+      <c r="C38" s="32" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="D38" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E38" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="26" t="inlineStr">
         <is>
           <t>水果</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B39" s="27" t="inlineStr">
         <is>
           <t>鸭梨</t>
         </is>
       </c>
-      <c r="C39" s="10" t="n">
+      <c r="C39" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="D39" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E39" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="30" t="inlineStr">
         <is>
           <t>水果</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="31" t="inlineStr">
         <is>
           <t>西瓜</t>
         </is>
       </c>
-      <c r="C40" s="6" t="n">
+      <c r="C40" s="32" t="n">
         <v>3.7</v>
       </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="D40" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E40" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="26" t="inlineStr">
         <is>
           <t>水果</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B41" s="27" t="inlineStr">
         <is>
           <t>进口莲雾</t>
         </is>
       </c>
-      <c r="C41" s="10" t="n">
+      <c r="C41" s="28" t="n">
         <v>22</v>
       </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="D41" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E41" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="30" t="inlineStr">
         <is>
           <t>水果</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" s="31" t="inlineStr">
         <is>
           <t>山竹</t>
         </is>
       </c>
-      <c r="C42" s="6" t="n">
+      <c r="C42" s="32" t="n">
         <v>17</v>
       </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="D42" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E42" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="26" t="inlineStr">
         <is>
           <t>水果</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B43" s="27" t="inlineStr">
         <is>
           <t>火龙果（白肉）</t>
         </is>
       </c>
-      <c r="C43" s="10" t="n">
+      <c r="C43" s="28" t="n">
         <v>6.8</v>
       </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="D43" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E43" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="30" t="inlineStr">
         <is>
           <t>水果</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" s="31" t="inlineStr">
         <is>
           <t>本地香蕉</t>
         </is>
       </c>
-      <c r="C44" s="6" t="n">
+      <c r="C44" s="32" t="n">
         <v>3.2</v>
       </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="D44" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E44" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="26" t="inlineStr">
         <is>
           <t>水果</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B45" s="27" t="inlineStr">
         <is>
           <t>本地菠萝</t>
         </is>
       </c>
-      <c r="C45" s="10" t="n">
+      <c r="C45" s="28" t="n">
         <v>6.3</v>
       </c>
-      <c r="D45" s="13" t="inlineStr">
+      <c r="D45" s="37" t="inlineStr">
         <is>
           <t>↓ -1.56%</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="E45" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="30" t="inlineStr">
         <is>
           <t>水果</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B46" s="31" t="inlineStr">
         <is>
           <t>荔枝（乌叶）</t>
         </is>
       </c>
-      <c r="C46" s="6" t="n">
+      <c r="C46" s="32" t="n">
         <v>9.33</v>
       </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="D46" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E46" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="18" t="inlineStr">
+      <c r="A47" s="25" t="inlineStr">
         <is>
           <t>📂 肉禽蛋（10 个品种）</t>
         </is>
@@ -1795,257 +1795,257 @@
       <c r="E47" s="21" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="30" t="inlineStr">
         <is>
           <t>肉禽蛋</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B48" s="31" t="inlineStr">
         <is>
           <t>猪瘦肉</t>
         </is>
       </c>
-      <c r="C48" s="6" t="n">
+      <c r="C48" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="D48" s="14" t="inlineStr">
+      <c r="D48" s="34" t="inlineStr">
         <is>
           <t>↑ +6.06%</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E48" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="26" t="inlineStr">
         <is>
           <t>肉禽蛋</t>
         </is>
       </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="B49" s="27" t="inlineStr">
         <is>
           <t>五花肉</t>
         </is>
       </c>
-      <c r="C49" s="10" t="n">
+      <c r="C49" s="28" t="n">
         <v>13.6</v>
       </c>
-      <c r="D49" s="12" t="inlineStr">
+      <c r="D49" s="36" t="inlineStr">
         <is>
           <t>↑ +6.25%</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
+      <c r="E49" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="30" t="inlineStr">
         <is>
           <t>肉禽蛋</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B50" s="31" t="inlineStr">
         <is>
           <t>带皮后腿肉</t>
         </is>
       </c>
-      <c r="C50" s="6" t="n">
+      <c r="C50" s="32" t="n">
         <v>8.6</v>
       </c>
-      <c r="D50" s="14" t="inlineStr">
+      <c r="D50" s="34" t="inlineStr">
         <is>
           <t>↑ +7.50%</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E50" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="26" t="inlineStr">
         <is>
           <t>肉禽蛋</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B51" s="27" t="inlineStr">
         <is>
           <t>排骨</t>
         </is>
       </c>
-      <c r="C51" s="10" t="n">
+      <c r="C51" s="28" t="n">
         <v>25.8</v>
       </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="D51" s="36" t="inlineStr">
         <is>
           <t>↑ +2.38%</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
+      <c r="E51" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="30" t="inlineStr">
         <is>
           <t>肉禽蛋</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B52" s="31" t="inlineStr">
         <is>
           <t>牛腱子肉</t>
         </is>
       </c>
-      <c r="C52" s="6" t="n">
+      <c r="C52" s="32" t="n">
         <v>45</v>
       </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="D52" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E52" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="26" t="inlineStr">
         <is>
           <t>肉禽蛋</t>
         </is>
       </c>
-      <c r="B53" s="9" t="inlineStr">
+      <c r="B53" s="27" t="inlineStr">
         <is>
           <t>牛腩</t>
         </is>
       </c>
-      <c r="C53" s="10" t="n">
+      <c r="C53" s="28" t="n">
         <v>42</v>
       </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr">
+      <c r="D53" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E53" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="30" t="inlineStr">
         <is>
           <t>肉禽蛋</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B54" s="31" t="inlineStr">
         <is>
           <t>白条鸡</t>
         </is>
       </c>
-      <c r="C54" s="6" t="n">
+      <c r="C54" s="32" t="n">
         <v>10.8</v>
       </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="D54" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E54" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="A55" s="26" t="inlineStr">
         <is>
           <t>肉禽蛋</t>
         </is>
       </c>
-      <c r="B55" s="9" t="inlineStr">
+      <c r="B55" s="27" t="inlineStr">
         <is>
           <t>白条鸭（菜鸭）</t>
         </is>
       </c>
-      <c r="C55" s="10" t="n">
+      <c r="C55" s="28" t="n">
         <v>10.6</v>
       </c>
-      <c r="D55" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E55" s="8" t="inlineStr">
+      <c r="D55" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E55" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="30" t="inlineStr">
         <is>
           <t>肉禽蛋</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B56" s="31" t="inlineStr">
         <is>
           <t>鸡场蛋</t>
         </is>
       </c>
-      <c r="C56" s="6" t="n">
+      <c r="C56" s="32" t="n">
         <v>6.6</v>
       </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="D56" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E56" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" s="26" t="inlineStr">
         <is>
           <t>肉禽蛋</t>
         </is>
       </c>
-      <c r="B57" s="9" t="inlineStr">
+      <c r="B57" s="27" t="inlineStr">
         <is>
           <t>鸭蛋</t>
         </is>
       </c>
-      <c r="C57" s="10" t="n">
+      <c r="C57" s="28" t="n">
         <v>6.4</v>
       </c>
-      <c r="D57" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E57" s="8" t="inlineStr">
+      <c r="D57" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E57" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="18" t="inlineStr">
+      <c r="A58" s="25" t="inlineStr">
         <is>
           <t>📂 水产（6 个品种）</t>
         </is>
@@ -2056,157 +2056,157 @@
       <c r="E58" s="21" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" s="26" t="inlineStr">
         <is>
           <t>水产</t>
         </is>
       </c>
-      <c r="B59" s="9" t="inlineStr">
+      <c r="B59" s="27" t="inlineStr">
         <is>
           <t>冻带鱼（250g）</t>
         </is>
       </c>
-      <c r="C59" s="10" t="n">
+      <c r="C59" s="28" t="n">
         <v>22.25</v>
       </c>
-      <c r="D59" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E59" s="8" t="inlineStr">
+      <c r="D59" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E59" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="30" t="inlineStr">
         <is>
           <t>水产</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B60" s="31" t="inlineStr">
         <is>
           <t>草鱼（1000g）</t>
         </is>
       </c>
-      <c r="C60" s="6" t="n">
+      <c r="C60" s="32" t="n">
         <v>10.25</v>
       </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="D60" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E60" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="inlineStr">
+      <c r="A61" s="26" t="inlineStr">
         <is>
           <t>水产</t>
         </is>
       </c>
-      <c r="B61" s="9" t="inlineStr">
+      <c r="B61" s="27" t="inlineStr">
         <is>
           <t>冻黄鱼（500g）</t>
         </is>
       </c>
-      <c r="C61" s="10" t="n">
+      <c r="C61" s="28" t="n">
         <v>26</v>
       </c>
-      <c r="D61" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E61" s="8" t="inlineStr">
+      <c r="D61" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E61" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="30" t="inlineStr">
         <is>
           <t>水产</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="B62" s="31" t="inlineStr">
         <is>
           <t>鳙鱼（1500g）</t>
         </is>
       </c>
-      <c r="C62" s="6" t="n">
+      <c r="C62" s="32" t="n">
         <v>13</v>
       </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="D62" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E62" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="A63" s="26" t="inlineStr">
         <is>
           <t>水产</t>
         </is>
       </c>
-      <c r="B63" s="9" t="inlineStr">
+      <c r="B63" s="27" t="inlineStr">
         <is>
           <t>白鲫鱼（350g）</t>
         </is>
       </c>
-      <c r="C63" s="10" t="n">
+      <c r="C63" s="28" t="n">
         <v>13.75</v>
       </c>
-      <c r="D63" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
+      <c r="D63" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E63" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="30" t="inlineStr">
         <is>
           <t>水产</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B64" s="31" t="inlineStr">
         <is>
           <t>活虾（10cm）</t>
         </is>
       </c>
-      <c r="C64" s="6" t="n">
+      <c r="C64" s="32" t="n">
         <v>28.2</v>
       </c>
-      <c r="D64" s="14" t="inlineStr">
+      <c r="D64" s="34" t="inlineStr">
         <is>
           <t>↑ +0.71%</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="E64" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="65" ht="24" customHeight="1">
-      <c r="A65" s="18" t="inlineStr">
+      <c r="A65" s="25" t="inlineStr">
         <is>
           <t>📂 粮油（24 个品种）</t>
         </is>
@@ -2217,607 +2217,607 @@
       <c r="E65" s="21" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="30" t="inlineStr">
         <is>
           <t>粮油</t>
         </is>
       </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="B66" s="31" t="inlineStr">
         <is>
           <t>黄豆</t>
         </is>
       </c>
-      <c r="C66" s="6" t="n">
+      <c r="C66" s="32" t="n">
         <v>5.2</v>
       </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="D66" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E66" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="inlineStr">
+      <c r="A67" s="26" t="inlineStr">
         <is>
           <t>粮油</t>
         </is>
       </c>
-      <c r="B67" s="9" t="inlineStr">
+      <c r="B67" s="27" t="inlineStr">
         <is>
           <t>绿豆</t>
         </is>
       </c>
-      <c r="C67" s="10" t="n">
+      <c r="C67" s="28" t="n">
         <v>7.2</v>
       </c>
-      <c r="D67" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E67" s="8" t="inlineStr">
+      <c r="D67" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E67" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="30" t="inlineStr">
         <is>
           <t>粮油</t>
         </is>
       </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="B68" s="31" t="inlineStr">
         <is>
           <t>晚籼米（煮干饭）</t>
         </is>
       </c>
-      <c r="C68" s="6" t="n">
+      <c r="C68" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="D68" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="inlineStr">
+      <c r="A69" s="26" t="inlineStr">
         <is>
           <t>粮油</t>
         </is>
       </c>
-      <c r="B69" s="9" t="inlineStr">
+      <c r="B69" s="27" t="inlineStr">
         <is>
           <t>粳米（珍珠米煮稀饭）</t>
         </is>
       </c>
-      <c r="C69" s="10" t="n">
+      <c r="C69" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="D69" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E69" s="8" t="inlineStr">
+      <c r="D69" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E69" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>粮油</t>
         </is>
       </c>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="B70" s="31" t="inlineStr">
         <is>
           <t>东北米（珍珠米）5公斤小包装</t>
         </is>
       </c>
-      <c r="C70" s="6" t="n">
+      <c r="C70" s="32" t="n">
         <v>34.6</v>
       </c>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="D70" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="inlineStr">
+      <c r="A71" s="26" t="inlineStr">
         <is>
           <t>粮油</t>
         </is>
       </c>
-      <c r="B71" s="9" t="inlineStr">
+      <c r="B71" s="27" t="inlineStr">
         <is>
           <t>面粉（标准粉）</t>
         </is>
       </c>
-      <c r="C71" s="10" t="n">
+      <c r="C71" s="28" t="n">
         <v>2.6</v>
       </c>
-      <c r="D71" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E71" s="8" t="inlineStr">
+      <c r="D71" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E71" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="A72" s="30" t="inlineStr">
         <is>
           <t>粮油</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B72" s="31" t="inlineStr">
         <is>
           <t>菜籽油（5L/桶）金龙鱼</t>
         </is>
       </c>
-      <c r="C72" s="6" t="n">
+      <c r="C72" s="32" t="n">
         <v>70</v>
       </c>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
+      <c r="D72" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E72" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="inlineStr">
+      <c r="A73" s="26" t="inlineStr">
         <is>
           <t>粮油</t>
         </is>
       </c>
-      <c r="B73" s="9" t="inlineStr">
+      <c r="B73" s="27" t="inlineStr">
         <is>
           <t>大豆油（5L/桶）金龙鱼</t>
         </is>
       </c>
-      <c r="C73" s="10" t="n">
+      <c r="C73" s="28" t="n">
         <v>63.75</v>
       </c>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="inlineStr">
+      <c r="D73" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E73" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="A74" s="30" t="inlineStr">
         <is>
           <t>粮油</t>
         </is>
       </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="B74" s="31" t="inlineStr">
         <is>
           <t>花生油（5L/桶）金龙鱼</t>
         </is>
       </c>
-      <c r="C74" s="6" t="n">
+      <c r="C74" s="32" t="n">
         <v>100</v>
       </c>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="D74" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E74" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="inlineStr">
+      <c r="A75" s="26" t="inlineStr">
         <is>
           <t>粮油</t>
         </is>
       </c>
-      <c r="B75" s="9" t="inlineStr">
+      <c r="B75" s="27" t="inlineStr">
         <is>
           <t>第二代食用调和油（5L/桶）金龙鱼</t>
         </is>
       </c>
-      <c r="C75" s="10" t="n">
+      <c r="C75" s="28" t="n">
         <v>65</v>
       </c>
-      <c r="D75" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="inlineStr">
+      <c r="D75" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E75" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="30" t="inlineStr">
         <is>
           <t>粮油</t>
         </is>
       </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="B76" s="31" t="inlineStr">
         <is>
           <t>鲁花花生油（5L/桶）</t>
         </is>
       </c>
-      <c r="C76" s="6" t="n">
+      <c r="C76" s="32" t="n">
         <v>150</v>
       </c>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
+      <c r="D76" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="8" t="inlineStr">
+      <c r="A77" s="26" t="inlineStr">
         <is>
           <t>粮油</t>
         </is>
       </c>
-      <c r="B77" s="9" t="inlineStr">
+      <c r="B77" s="27" t="inlineStr">
         <is>
           <t>金鼠香米（斤）</t>
         </is>
       </c>
-      <c r="C77" s="10" t="n">
+      <c r="C77" s="28" t="n">
         <v>3.7</v>
       </c>
-      <c r="D77" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
+      <c r="D77" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E77" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>粮油</t>
         </is>
       </c>
-      <c r="B78" s="5" t="inlineStr">
+      <c r="B78" s="31" t="inlineStr">
         <is>
           <t>广洋湖香粘米（斤）</t>
         </is>
       </c>
-      <c r="C78" s="6" t="n">
+      <c r="C78" s="32" t="n">
         <v>4.2</v>
       </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="D78" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E78" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="inlineStr">
+      <c r="A79" s="26" t="inlineStr">
         <is>
           <t>粮油</t>
         </is>
       </c>
-      <c r="B79" s="9" t="inlineStr">
+      <c r="B79" s="27" t="inlineStr">
         <is>
           <t>盘锦大米（斤）</t>
         </is>
       </c>
-      <c r="C79" s="10" t="n">
+      <c r="C79" s="28" t="n">
         <v>4.2</v>
       </c>
-      <c r="D79" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E79" s="8" t="inlineStr">
+      <c r="D79" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E79" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="A80" s="30" t="inlineStr">
         <is>
           <t>粮油</t>
         </is>
       </c>
-      <c r="B80" s="5" t="inlineStr">
+      <c r="B80" s="31" t="inlineStr">
         <is>
           <t>洪家鸡油粘香米（5KG/包）</t>
         </is>
       </c>
-      <c r="C80" s="6" t="n">
+      <c r="C80" s="32" t="n">
         <v>39</v>
       </c>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="D80" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E80" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="8" t="inlineStr">
+      <c r="A81" s="26" t="inlineStr">
         <is>
           <t>粮油</t>
         </is>
       </c>
-      <c r="B81" s="9" t="inlineStr">
+      <c r="B81" s="27" t="inlineStr">
         <is>
           <t>十月稻田长粒香米（5KG/包）</t>
         </is>
       </c>
-      <c r="C81" s="10" t="n">
+      <c r="C81" s="28" t="n">
         <v>70</v>
       </c>
-      <c r="D81" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E81" s="8" t="inlineStr">
+      <c r="D81" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E81" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="A82" s="30" t="inlineStr">
         <is>
           <t>粮油</t>
         </is>
       </c>
-      <c r="B82" s="5" t="inlineStr">
+      <c r="B82" s="31" t="inlineStr">
         <is>
           <t>十月稻田香稻贡米（5KG/包）</t>
         </is>
       </c>
-      <c r="C82" s="6" t="n">
+      <c r="C82" s="32" t="n">
         <v>79.90000000000001</v>
       </c>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
+      <c r="D82" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E82" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="8" t="inlineStr">
+      <c r="A83" s="26" t="inlineStr">
         <is>
           <t>粮油</t>
         </is>
       </c>
-      <c r="B83" s="9" t="inlineStr">
+      <c r="B83" s="27" t="inlineStr">
         <is>
           <t>小悦米（5KG/包）</t>
         </is>
       </c>
-      <c r="C83" s="10" t="n">
+      <c r="C83" s="28" t="n">
         <v>48</v>
       </c>
-      <c r="D83" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E83" s="8" t="inlineStr">
+      <c r="D83" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E83" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="A84" s="30" t="inlineStr">
         <is>
           <t>粮油</t>
         </is>
       </c>
-      <c r="B84" s="5" t="inlineStr">
+      <c r="B84" s="31" t="inlineStr">
         <is>
           <t>九三非转基因大豆油（10L/桶）</t>
         </is>
       </c>
-      <c r="C84" s="6" t="n">
+      <c r="C84" s="32" t="n">
         <v>160</v>
       </c>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
+      <c r="D84" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E84" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="8" t="inlineStr">
+      <c r="A85" s="26" t="inlineStr">
         <is>
           <t>粮油</t>
         </is>
       </c>
-      <c r="B85" s="9" t="inlineStr">
+      <c r="B85" s="27" t="inlineStr">
         <is>
           <t>九三压榨浓香花生油（5L/桶）</t>
         </is>
       </c>
-      <c r="C85" s="10" t="n">
+      <c r="C85" s="28" t="n">
         <v>158</v>
       </c>
-      <c r="D85" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E85" s="8" t="inlineStr">
+      <c r="D85" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E85" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="inlineStr">
+      <c r="A86" s="30" t="inlineStr">
         <is>
           <t>粮油</t>
         </is>
       </c>
-      <c r="B86" s="5" t="inlineStr">
+      <c r="B86" s="31" t="inlineStr">
         <is>
           <t>馒头粉（斤）</t>
         </is>
       </c>
-      <c r="C86" s="6" t="n">
+      <c r="C86" s="32" t="n">
         <v>3.1</v>
       </c>
-      <c r="D86" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="inlineStr">
+      <c r="D86" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E86" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="8" t="inlineStr">
+      <c r="A87" s="26" t="inlineStr">
         <is>
           <t>粮油</t>
         </is>
       </c>
-      <c r="B87" s="9" t="inlineStr">
+      <c r="B87" s="27" t="inlineStr">
         <is>
           <t>玉米淀粉（斤）</t>
         </is>
       </c>
-      <c r="C87" s="10" t="n">
+      <c r="C87" s="28" t="n">
         <v>3.7</v>
       </c>
-      <c r="D87" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E87" s="8" t="inlineStr">
+      <c r="D87" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E87" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="A88" s="30" t="inlineStr">
         <is>
           <t>粮油</t>
         </is>
       </c>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="B88" s="31" t="inlineStr">
         <is>
           <t>大树碱面（1500g/件）</t>
         </is>
       </c>
-      <c r="C88" s="6" t="n">
+      <c r="C88" s="32" t="n">
         <v>41</v>
       </c>
-      <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr">
+      <c r="D88" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E88" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="inlineStr">
+      <c r="A89" s="26" t="inlineStr">
         <is>
           <t>粮油</t>
         </is>
       </c>
-      <c r="B89" s="9" t="inlineStr">
+      <c r="B89" s="27" t="inlineStr">
         <is>
           <t>糯米</t>
         </is>
       </c>
-      <c r="C89" s="10" t="n">
+      <c r="C89" s="28" t="n">
         <v>4.8</v>
       </c>
-      <c r="D89" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E89" s="8" t="inlineStr">
+      <c r="D89" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E89" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="90" ht="24" customHeight="1">
-      <c r="A90" s="18" t="inlineStr">
+      <c r="A90" s="25" t="inlineStr">
         <is>
           <t>📂 其它（7 个品种）</t>
         </is>
@@ -2828,191 +2828,191 @@
       <c r="E90" s="21" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="8" t="inlineStr">
+      <c r="A91" s="26" t="inlineStr">
         <is>
           <t>其它</t>
         </is>
       </c>
-      <c r="B91" s="9" t="inlineStr">
+      <c r="B91" s="27" t="inlineStr">
         <is>
           <t>水豆腐（块）</t>
         </is>
       </c>
-      <c r="C91" s="10" t="n">
+      <c r="C91" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="D91" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E91" s="8" t="inlineStr">
+      <c r="D91" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E91" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="inlineStr">
+      <c r="A92" s="30" t="inlineStr">
         <is>
           <t>其它</t>
         </is>
       </c>
-      <c r="B92" s="5" t="inlineStr">
+      <c r="B92" s="31" t="inlineStr">
         <is>
           <t>晶华自然盐（400g/袋）</t>
         </is>
       </c>
-      <c r="C92" s="6" t="n">
+      <c r="C92" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D92" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
+      <c r="D92" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E92" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="8" t="inlineStr">
+      <c r="A93" s="26" t="inlineStr">
         <is>
           <t>其它</t>
         </is>
       </c>
-      <c r="B93" s="9" t="inlineStr">
+      <c r="B93" s="27" t="inlineStr">
         <is>
           <t>冰度白砂糖（400g/袋）</t>
         </is>
       </c>
-      <c r="C93" s="10" t="n">
+      <c r="C93" s="28" t="n">
         <v>4.9</v>
       </c>
-      <c r="D93" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E93" s="8" t="inlineStr">
+      <c r="D93" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E93" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="A94" s="30" t="inlineStr">
         <is>
           <t>其它</t>
         </is>
       </c>
-      <c r="B94" s="5" t="inlineStr">
+      <c r="B94" s="31" t="inlineStr">
         <is>
           <t>冰度红糖（400g/袋）</t>
         </is>
       </c>
-      <c r="C94" s="6" t="n">
+      <c r="C94" s="32" t="n">
         <v>5.4</v>
       </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E94" s="4" t="inlineStr">
+      <c r="D94" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E94" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="8" t="inlineStr">
+      <c r="A95" s="26" t="inlineStr">
         <is>
           <t>其它</t>
         </is>
       </c>
-      <c r="B95" s="9" t="inlineStr">
+      <c r="B95" s="27" t="inlineStr">
         <is>
           <t>恒顺陈醋（500ml/瓶）</t>
         </is>
       </c>
-      <c r="C95" s="10" t="n">
+      <c r="C95" s="28" t="n">
         <v>6.6</v>
       </c>
-      <c r="D95" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E95" s="8" t="inlineStr">
+      <c r="D95" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E95" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="A96" s="30" t="inlineStr">
         <is>
           <t>其它</t>
         </is>
       </c>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="B96" s="31" t="inlineStr">
         <is>
           <t>蜜蜂味精（454g/袋）</t>
         </is>
       </c>
-      <c r="C96" s="6" t="n">
+      <c r="C96" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E96" s="4" t="inlineStr">
+      <c r="D96" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E96" s="30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="8" t="inlineStr">
+      <c r="A97" s="26" t="inlineStr">
         <is>
           <t>其它</t>
         </is>
       </c>
-      <c r="B97" s="9" t="inlineStr">
+      <c r="B97" s="27" t="inlineStr">
         <is>
           <t>香菇</t>
         </is>
       </c>
-      <c r="C97" s="10" t="n">
+      <c r="C97" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="D97" s="11" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E97" s="8" t="inlineStr">
+      <c r="D97" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E97" s="26" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="15" t="inlineStr">
-        <is>
-          <t>📊 共 88 个品种 | 上涨 12 个 | 下跌 2 个 | 持平 74 个</t>
+      <c r="A99" s="38" t="inlineStr">
+        <is>
+          <t>📊 共 88 个品种 | 上涨 12 | 下跌 2 | 持平 74 | 无对比 0</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="16" t="inlineStr">
-        <is>
-          <t>↑ 红色=价格上涨  ↓ 绿色=价格下跌  → 灰色=持平  — =无上日数据</t>
+      <c r="A100" s="39" t="inlineStr">
+        <is>
+          <t>↑ 红色=涨  ↓ 绿色=跌  → 灰色=持平  — =无上日数据</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3093,7 +3093,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="25" t="inlineStr">
         <is>
-          <t>📂 水果（9 个品种）</t>
+          <t>📂 蔬菜（32 个品种）</t>
         </is>
       </c>
       <c r="B4" s="19" t="n"/>
@@ -3104,16 +3104,16 @@
     <row r="5">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>水果</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>富士苹果</t>
+          <t>老姜</t>
         </is>
       </c>
       <c r="C5" s="28" t="n">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="D5" s="29" t="inlineStr">
         <is>
@@ -3129,16 +3129,16 @@
     <row r="6">
       <c r="A6" s="30" t="inlineStr">
         <is>
-          <t>水果</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B6" s="31" t="inlineStr">
         <is>
-          <t>鸭梨</t>
+          <t>蒜头</t>
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="D6" s="33" t="inlineStr">
         <is>
@@ -3154,20 +3154,20 @@
     <row r="7">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>水果</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>西瓜</t>
+          <t>葱</t>
         </is>
       </c>
       <c r="C7" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" s="34" t="inlineStr">
-        <is>
-          <t>↓ -2.44%</t>
+        <v>6.4</v>
+      </c>
+      <c r="D7" s="36" t="inlineStr">
+        <is>
+          <t>↑ +3.23%</t>
         </is>
       </c>
       <c r="E7" s="26" t="inlineStr">
@@ -3179,20 +3179,20 @@
     <row r="8">
       <c r="A8" s="30" t="inlineStr">
         <is>
-          <t>水果</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B8" s="31" t="inlineStr">
         <is>
-          <t>进口莲雾</t>
+          <t>芹菜</t>
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>25</v>
-      </c>
-      <c r="D8" s="33" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
+        <v>6.8</v>
+      </c>
+      <c r="D8" s="34" t="inlineStr">
+        <is>
+          <t>↑ +3.03%</t>
         </is>
       </c>
       <c r="E8" s="30" t="inlineStr">
@@ -3204,20 +3204,20 @@
     <row r="9">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>水果</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>山竹</t>
+          <t>大白菜</t>
         </is>
       </c>
       <c r="C9" s="28" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="D9" s="34" t="inlineStr">
-        <is>
-          <t>↓ -2.27%</t>
+        <v>2.7</v>
+      </c>
+      <c r="D9" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
         </is>
       </c>
       <c r="E9" s="26" t="inlineStr">
@@ -3229,20 +3229,20 @@
     <row r="10">
       <c r="A10" s="30" t="inlineStr">
         <is>
-          <t>水果</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B10" s="31" t="inlineStr">
         <is>
-          <t>火龙果（白肉）</t>
+          <t>上海青</t>
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="D10" s="33" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
+        <v>4.4</v>
+      </c>
+      <c r="D10" s="35" t="inlineStr">
+        <is>
+          <t>↓ -4.35%</t>
         </is>
       </c>
       <c r="E10" s="30" t="inlineStr">
@@ -3254,12 +3254,12 @@
     <row r="11">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>水果</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B11" s="27" t="inlineStr">
         <is>
-          <t>本地香蕉</t>
+          <t>黄瓜</t>
         </is>
       </c>
       <c r="C11" s="28" t="n">
@@ -3279,20 +3279,20 @@
     <row r="12">
       <c r="A12" s="30" t="inlineStr">
         <is>
-          <t>水果</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B12" s="31" t="inlineStr">
         <is>
-          <t>本地菠萝</t>
+          <t>白萝卜</t>
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="D12" s="35" t="inlineStr">
-        <is>
-          <t>↑ +1.69%</t>
+        <v>2.5</v>
+      </c>
+      <c r="D12" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
         </is>
       </c>
       <c r="E12" s="30" t="inlineStr">
@@ -3304,16 +3304,16 @@
     <row r="13">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>水果</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B13" s="27" t="inlineStr">
         <is>
-          <t>荔枝（乌叶）</t>
+          <t>长茄</t>
         </is>
       </c>
       <c r="C13" s="28" t="n">
-        <v>10.33</v>
+        <v>4.8</v>
       </c>
       <c r="D13" s="29" t="inlineStr">
         <is>
@@ -3326,30 +3326,44 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="25" t="inlineStr">
-        <is>
-          <t>📂 肉禽蛋（10 个品种）</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="n"/>
-      <c r="C14" s="19" t="n"/>
-      <c r="D14" s="19" t="n"/>
-      <c r="E14" s="19" t="n"/>
+    <row r="14">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="inlineStr">
+        <is>
+          <t>西红柿</t>
+        </is>
+      </c>
+      <c r="C14" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D14" s="35" t="inlineStr">
+        <is>
+          <t>↓ -2.17%</t>
+        </is>
+      </c>
+      <c r="E14" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>肉禽蛋</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t>猪瘦肉</t>
+          <t>土豆</t>
         </is>
       </c>
       <c r="C15" s="28" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D15" s="29" t="inlineStr">
         <is>
@@ -3365,16 +3379,16 @@
     <row r="16">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>肉禽蛋</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B16" s="31" t="inlineStr">
         <is>
-          <t>五花肉</t>
+          <t>胡萝卜</t>
         </is>
       </c>
       <c r="C16" s="32" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D16" s="33" t="inlineStr">
         <is>
@@ -3390,16 +3404,16 @@
     <row r="17">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>肉禽蛋</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>带皮后腿肉</t>
+          <t>青椒</t>
         </is>
       </c>
       <c r="C17" s="28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D17" s="29" t="inlineStr">
         <is>
@@ -3415,20 +3429,20 @@
     <row r="18">
       <c r="A18" s="30" t="inlineStr">
         <is>
-          <t>肉禽蛋</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B18" s="31" t="inlineStr">
         <is>
-          <t>排骨</t>
+          <t>尖椒</t>
         </is>
       </c>
       <c r="C18" s="32" t="n">
-        <v>25</v>
-      </c>
-      <c r="D18" s="36" t="inlineStr">
-        <is>
-          <t>↓ -0.79%</t>
+        <v>6</v>
+      </c>
+      <c r="D18" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
         </is>
       </c>
       <c r="E18" s="30" t="inlineStr">
@@ -3440,16 +3454,16 @@
     <row r="19">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>肉禽蛋</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B19" s="27" t="inlineStr">
         <is>
-          <t>牛腱子肉</t>
+          <t>包菜</t>
         </is>
       </c>
       <c r="C19" s="28" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="D19" s="29" t="inlineStr">
         <is>
@@ -3465,16 +3479,16 @@
     <row r="20">
       <c r="A20" s="30" t="inlineStr">
         <is>
-          <t>肉禽蛋</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B20" s="31" t="inlineStr">
         <is>
-          <t>牛腩</t>
+          <t>蒜苔</t>
         </is>
       </c>
       <c r="C20" s="32" t="n">
-        <v>42</v>
+        <v>7.3</v>
       </c>
       <c r="D20" s="33" t="inlineStr">
         <is>
@@ -3490,16 +3504,16 @@
     <row r="21">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>肉禽蛋</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B21" s="27" t="inlineStr">
         <is>
-          <t>白条鸡</t>
+          <t>花菜</t>
         </is>
       </c>
       <c r="C21" s="28" t="n">
-        <v>11.4</v>
+        <v>4.8</v>
       </c>
       <c r="D21" s="29" t="inlineStr">
         <is>
@@ -3515,16 +3529,16 @@
     <row r="22">
       <c r="A22" s="30" t="inlineStr">
         <is>
-          <t>肉禽蛋</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B22" s="31" t="inlineStr">
         <is>
-          <t>白条鸭（菜鸭）</t>
+          <t>韭菜</t>
         </is>
       </c>
       <c r="C22" s="32" t="n">
-        <v>10.4</v>
+        <v>4.5</v>
       </c>
       <c r="D22" s="33" t="inlineStr">
         <is>
@@ -3540,20 +3554,20 @@
     <row r="23">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>肉禽蛋</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B23" s="27" t="inlineStr">
         <is>
-          <t>鸡场蛋</t>
+          <t>空心菜</t>
         </is>
       </c>
       <c r="C23" s="28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="D23" s="29" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
+        <v>5.1</v>
+      </c>
+      <c r="D23" s="36" t="inlineStr">
+        <is>
+          <t>↑ +13.33%</t>
         </is>
       </c>
       <c r="E23" s="26" t="inlineStr">
@@ -3565,20 +3579,20 @@
     <row r="24">
       <c r="A24" s="30" t="inlineStr">
         <is>
-          <t>肉禽蛋</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B24" s="31" t="inlineStr">
         <is>
-          <t>鸭蛋</t>
+          <t>绿豆芽</t>
         </is>
       </c>
       <c r="C24" s="32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D24" s="35" t="inlineStr">
-        <is>
-          <t>↑ +1.56%</t>
+        <v>2.1</v>
+      </c>
+      <c r="D24" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
         </is>
       </c>
       <c r="E24" s="30" t="inlineStr">
@@ -3587,30 +3601,44 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
-        <is>
-          <t>📂 水产（6 个品种）</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="n"/>
-      <c r="C25" s="19" t="n"/>
-      <c r="D25" s="19" t="n"/>
-      <c r="E25" s="19" t="n"/>
+    <row r="25">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B25" s="27" t="inlineStr">
+        <is>
+          <t>油菜</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D25" s="37" t="inlineStr">
+        <is>
+          <t>↓ -2.08%</t>
+        </is>
+      </c>
+      <c r="E25" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="30" t="inlineStr">
         <is>
-          <t>水产</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B26" s="31" t="inlineStr">
         <is>
-          <t>冻带鱼（250g）</t>
+          <t>油麦菜</t>
         </is>
       </c>
       <c r="C26" s="32" t="n">
-        <v>22.5</v>
+        <v>4.4</v>
       </c>
       <c r="D26" s="33" t="inlineStr">
         <is>
@@ -3626,16 +3654,16 @@
     <row r="27">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>水产</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>草鱼（1000g）</t>
+          <t>菠菜</t>
         </is>
       </c>
       <c r="C27" s="28" t="n">
-        <v>10.5</v>
+        <v>6.9</v>
       </c>
       <c r="D27" s="29" t="inlineStr">
         <is>
@@ -3651,20 +3679,20 @@
     <row r="28">
       <c r="A28" s="30" t="inlineStr">
         <is>
-          <t>水产</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B28" s="31" t="inlineStr">
         <is>
-          <t>冻黄鱼（500g）</t>
+          <t>生菜</t>
         </is>
       </c>
       <c r="C28" s="32" t="n">
-        <v>26</v>
-      </c>
-      <c r="D28" s="33" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
+        <v>4.1</v>
+      </c>
+      <c r="D28" s="34" t="inlineStr">
+        <is>
+          <t>↑ +2.50%</t>
         </is>
       </c>
       <c r="E28" s="30" t="inlineStr">
@@ -3676,20 +3704,20 @@
     <row r="29">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>水产</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>鳙鱼（1500g）</t>
+          <t>苋菜（红）</t>
         </is>
       </c>
       <c r="C29" s="28" t="n">
-        <v>13</v>
-      </c>
-      <c r="D29" s="29" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
+        <v>5</v>
+      </c>
+      <c r="D29" s="36" t="inlineStr">
+        <is>
+          <t>↑ +16.28%</t>
         </is>
       </c>
       <c r="E29" s="26" t="inlineStr">
@@ -3701,16 +3729,16 @@
     <row r="30">
       <c r="A30" s="30" t="inlineStr">
         <is>
-          <t>水产</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B30" s="31" t="inlineStr">
         <is>
-          <t>白鲫鱼（350g）</t>
+          <t>地瓜叶</t>
         </is>
       </c>
       <c r="C30" s="32" t="n">
-        <v>13.75</v>
+        <v>3</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -3726,20 +3754,20 @@
     <row r="31">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>水产</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>活虾（10cm）</t>
+          <t>西芹</t>
         </is>
       </c>
       <c r="C31" s="28" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="D31" s="37" t="inlineStr">
-        <is>
-          <t>↑ +0.70%</t>
+        <v>4.6</v>
+      </c>
+      <c r="D31" s="36" t="inlineStr">
+        <is>
+          <t>↑ +2.22%</t>
         </is>
       </c>
       <c r="E31" s="26" t="inlineStr">
@@ -3748,30 +3776,44 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="25" t="inlineStr">
-        <is>
-          <t>📂 粮油（24 个品种）</t>
-        </is>
-      </c>
-      <c r="B32" s="19" t="n"/>
-      <c r="C32" s="19" t="n"/>
-      <c r="D32" s="19" t="n"/>
-      <c r="E32" s="19" t="n"/>
+    <row r="32">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="B32" s="31" t="inlineStr">
+        <is>
+          <t>西兰花</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="D32" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E32" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>粮油</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>黄豆</t>
+          <t>本地芥菜</t>
         </is>
       </c>
       <c r="C33" s="28" t="n">
-        <v>5.2</v>
+        <v>3.67</v>
       </c>
       <c r="D33" s="29" t="inlineStr">
         <is>
@@ -3787,16 +3829,16 @@
     <row r="34">
       <c r="A34" s="30" t="inlineStr">
         <is>
-          <t>粮油</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B34" s="31" t="inlineStr">
         <is>
-          <t>绿豆</t>
+          <t>莴笋</t>
         </is>
       </c>
       <c r="C34" s="32" t="n">
-        <v>7.3</v>
+        <v>3.7</v>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
@@ -3812,16 +3854,16 @@
     <row r="35">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>粮油</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>晚籼米（煮干饭）</t>
+          <t>冬瓜</t>
         </is>
       </c>
       <c r="C35" s="28" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="D35" s="29" t="inlineStr">
         <is>
@@ -3837,20 +3879,20 @@
     <row r="36">
       <c r="A36" s="30" t="inlineStr">
         <is>
-          <t>粮油</t>
+          <t>蔬菜</t>
         </is>
       </c>
       <c r="B36" s="31" t="inlineStr">
         <is>
-          <t>粳米（珍珠米煮稀饭）</t>
+          <t>角瓜</t>
         </is>
       </c>
       <c r="C36" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="D36" s="33" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
+        <v>5.9</v>
+      </c>
+      <c r="D36" s="34" t="inlineStr">
+        <is>
+          <t>↑ +1.72%</t>
         </is>
       </c>
       <c r="E36" s="30" t="inlineStr">
@@ -3859,48 +3901,34 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="26" t="inlineStr">
-        <is>
-          <t>粮油</t>
-        </is>
-      </c>
-      <c r="B37" s="27" t="inlineStr">
-        <is>
-          <t>东北米（珍珠米）5公斤小包装</t>
-        </is>
-      </c>
-      <c r="C37" s="28" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="D37" s="29" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E37" s="26" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>📂 水果（9 个品种）</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="n"/>
+      <c r="C37" s="19" t="n"/>
+      <c r="D37" s="19" t="n"/>
+      <c r="E37" s="19" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="30" t="inlineStr">
         <is>
-          <t>粮油</t>
+          <t>水果</t>
         </is>
       </c>
       <c r="B38" s="31" t="inlineStr">
         <is>
-          <t>面粉（标准粉）</t>
+          <t>富士苹果</t>
         </is>
       </c>
       <c r="C38" s="32" t="n">
-        <v>2.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D38" s="33" t="inlineStr">
         <is>
-          <t>→ 0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E38" s="30" t="inlineStr">
@@ -3912,20 +3940,20 @@
     <row r="39">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>粮油</t>
+          <t>水果</t>
         </is>
       </c>
       <c r="B39" s="27" t="inlineStr">
         <is>
-          <t>菜籽油（5L/桶）金龙鱼</t>
+          <t>鸭梨</t>
         </is>
       </c>
       <c r="C39" s="28" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="D39" s="29" t="inlineStr">
         <is>
-          <t>→ 0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E39" s="26" t="inlineStr">
@@ -3937,20 +3965,20 @@
     <row r="40">
       <c r="A40" s="30" t="inlineStr">
         <is>
-          <t>粮油</t>
+          <t>水果</t>
         </is>
       </c>
       <c r="B40" s="31" t="inlineStr">
         <is>
-          <t>大豆油（5L/桶）金龙鱼</t>
+          <t>西瓜</t>
         </is>
       </c>
       <c r="C40" s="32" t="n">
-        <v>63.75</v>
+        <v>4</v>
       </c>
       <c r="D40" s="33" t="inlineStr">
         <is>
-          <t>→ 0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E40" s="30" t="inlineStr">
@@ -3962,20 +3990,20 @@
     <row r="41">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>粮油</t>
+          <t>水果</t>
         </is>
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>花生油（5L/桶）金龙鱼</t>
+          <t>进口莲雾</t>
         </is>
       </c>
       <c r="C41" s="28" t="n">
-        <v>100</v>
-      </c>
-      <c r="D41" s="34" t="inlineStr">
-        <is>
-          <t>↓ -1.64%</t>
+        <v>25</v>
+      </c>
+      <c r="D41" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="E41" s="26" t="inlineStr">
@@ -3987,20 +4015,20 @@
     <row r="42">
       <c r="A42" s="30" t="inlineStr">
         <is>
-          <t>粮油</t>
+          <t>水果</t>
         </is>
       </c>
       <c r="B42" s="31" t="inlineStr">
         <is>
-          <t>第二代食用调和油（5L/桶）金龙鱼</t>
+          <t>山竹</t>
         </is>
       </c>
       <c r="C42" s="32" t="n">
-        <v>65</v>
+        <v>17.2</v>
       </c>
       <c r="D42" s="33" t="inlineStr">
         <is>
-          <t>→ 0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E42" s="30" t="inlineStr">
@@ -4012,20 +4040,20 @@
     <row r="43">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>粮油</t>
+          <t>水果</t>
         </is>
       </c>
       <c r="B43" s="27" t="inlineStr">
         <is>
-          <t>鲁花花生油（5L/桶）</t>
+          <t>火龙果（白肉）</t>
         </is>
       </c>
       <c r="C43" s="28" t="n">
-        <v>150</v>
+        <v>6.7</v>
       </c>
       <c r="D43" s="29" t="inlineStr">
         <is>
-          <t>→ 0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E43" s="26" t="inlineStr">
@@ -4037,20 +4065,20 @@
     <row r="44">
       <c r="A44" s="30" t="inlineStr">
         <is>
-          <t>粮油</t>
+          <t>水果</t>
         </is>
       </c>
       <c r="B44" s="31" t="inlineStr">
         <is>
-          <t>金鼠香米（斤）</t>
+          <t>本地香蕉</t>
         </is>
       </c>
       <c r="C44" s="32" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="D44" s="33" t="inlineStr">
         <is>
-          <t>→ 0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E44" s="30" t="inlineStr">
@@ -4062,20 +4090,20 @@
     <row r="45">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>粮油</t>
+          <t>水果</t>
         </is>
       </c>
       <c r="B45" s="27" t="inlineStr">
         <is>
-          <t>广洋湖香粘米（斤）</t>
+          <t>本地菠萝</t>
         </is>
       </c>
       <c r="C45" s="28" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="D45" s="29" t="inlineStr">
         <is>
-          <t>→ 0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E45" s="26" t="inlineStr">
@@ -4087,20 +4115,20 @@
     <row r="46">
       <c r="A46" s="30" t="inlineStr">
         <is>
-          <t>粮油</t>
+          <t>水果</t>
         </is>
       </c>
       <c r="B46" s="31" t="inlineStr">
         <is>
-          <t>盘锦大米（斤）</t>
+          <t>荔枝（乌叶）</t>
         </is>
       </c>
       <c r="C46" s="32" t="n">
-        <v>4.2</v>
+        <v>10.33</v>
       </c>
       <c r="D46" s="33" t="inlineStr">
         <is>
-          <t>→ 0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E46" s="30" t="inlineStr">
@@ -4109,44 +4137,30 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="26" t="inlineStr">
-        <is>
-          <t>粮油</t>
-        </is>
-      </c>
-      <c r="B47" s="27" t="inlineStr">
-        <is>
-          <t>洪家鸡油粘香米（5KG/包）</t>
-        </is>
-      </c>
-      <c r="C47" s="28" t="n">
-        <v>39</v>
-      </c>
-      <c r="D47" s="29" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E47" s="26" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>📂 肉禽蛋（10 个品种）</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="n"/>
+      <c r="C47" s="19" t="n"/>
+      <c r="D47" s="19" t="n"/>
+      <c r="E47" s="19" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="30" t="inlineStr">
         <is>
-          <t>粮油</t>
+          <t>肉禽蛋</t>
         </is>
       </c>
       <c r="B48" s="31" t="inlineStr">
         <is>
-          <t>十月稻田长粒香米（5KG/包）</t>
+          <t>猪瘦肉</t>
         </is>
       </c>
       <c r="C48" s="32" t="n">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="D48" s="33" t="inlineStr">
         <is>
@@ -4162,16 +4176,16 @@
     <row r="49">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>粮油</t>
+          <t>肉禽蛋</t>
         </is>
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>十月稻田香稻贡米（5KG/包）</t>
+          <t>五花肉</t>
         </is>
       </c>
       <c r="C49" s="28" t="n">
-        <v>79.90000000000001</v>
+        <v>13</v>
       </c>
       <c r="D49" s="29" t="inlineStr">
         <is>
@@ -4187,16 +4201,16 @@
     <row r="50">
       <c r="A50" s="30" t="inlineStr">
         <is>
-          <t>粮油</t>
+          <t>肉禽蛋</t>
         </is>
       </c>
       <c r="B50" s="31" t="inlineStr">
         <is>
-          <t>小悦米（5KG/包）</t>
+          <t>带皮后腿肉</t>
         </is>
       </c>
       <c r="C50" s="32" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="D50" s="33" t="inlineStr">
         <is>
@@ -4212,20 +4226,20 @@
     <row r="51">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>粮油</t>
+          <t>肉禽蛋</t>
         </is>
       </c>
       <c r="B51" s="27" t="inlineStr">
         <is>
-          <t>九三非转基因大豆油（10L/桶）</t>
+          <t>排骨</t>
         </is>
       </c>
       <c r="C51" s="28" t="n">
-        <v>160</v>
-      </c>
-      <c r="D51" s="29" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
+        <v>25</v>
+      </c>
+      <c r="D51" s="37" t="inlineStr">
+        <is>
+          <t>↓ -0.79%</t>
         </is>
       </c>
       <c r="E51" s="26" t="inlineStr">
@@ -4237,16 +4251,16 @@
     <row r="52">
       <c r="A52" s="30" t="inlineStr">
         <is>
-          <t>粮油</t>
+          <t>肉禽蛋</t>
         </is>
       </c>
       <c r="B52" s="31" t="inlineStr">
         <is>
-          <t>九三压榨浓香花生油（5L/桶）</t>
+          <t>牛腱子肉</t>
         </is>
       </c>
       <c r="C52" s="32" t="n">
-        <v>158</v>
+        <v>45</v>
       </c>
       <c r="D52" s="33" t="inlineStr">
         <is>
@@ -4262,16 +4276,16 @@
     <row r="53">
       <c r="A53" s="26" t="inlineStr">
         <is>
-          <t>粮油</t>
+          <t>肉禽蛋</t>
         </is>
       </c>
       <c r="B53" s="27" t="inlineStr">
         <is>
-          <t>馒头粉（斤）</t>
+          <t>牛腩</t>
         </is>
       </c>
       <c r="C53" s="28" t="n">
-        <v>3.1</v>
+        <v>42</v>
       </c>
       <c r="D53" s="29" t="inlineStr">
         <is>
@@ -4287,16 +4301,16 @@
     <row r="54">
       <c r="A54" s="30" t="inlineStr">
         <is>
-          <t>粮油</t>
+          <t>肉禽蛋</t>
         </is>
       </c>
       <c r="B54" s="31" t="inlineStr">
         <is>
-          <t>玉米淀粉（斤）</t>
+          <t>白条鸡</t>
         </is>
       </c>
       <c r="C54" s="32" t="n">
-        <v>3.7</v>
+        <v>11.4</v>
       </c>
       <c r="D54" s="33" t="inlineStr">
         <is>
@@ -4312,16 +4326,16 @@
     <row r="55">
       <c r="A55" s="26" t="inlineStr">
         <is>
-          <t>粮油</t>
+          <t>肉禽蛋</t>
         </is>
       </c>
       <c r="B55" s="27" t="inlineStr">
         <is>
-          <t>大树碱面（1500g/件）</t>
+          <t>白条鸭（菜鸭）</t>
         </is>
       </c>
       <c r="C55" s="28" t="n">
-        <v>41</v>
+        <v>10.4</v>
       </c>
       <c r="D55" s="29" t="inlineStr">
         <is>
@@ -4337,16 +4351,16 @@
     <row r="56">
       <c r="A56" s="30" t="inlineStr">
         <is>
-          <t>粮油</t>
+          <t>肉禽蛋</t>
         </is>
       </c>
       <c r="B56" s="31" t="inlineStr">
         <is>
-          <t>糯米</t>
+          <t>鸡场蛋</t>
         </is>
       </c>
       <c r="C56" s="32" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="D56" s="33" t="inlineStr">
         <is>
@@ -4359,55 +4373,55 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="25" t="inlineStr">
-        <is>
-          <t>📂 其它（7 个品种）</t>
-        </is>
-      </c>
-      <c r="B57" s="19" t="n"/>
-      <c r="C57" s="19" t="n"/>
-      <c r="D57" s="19" t="n"/>
-      <c r="E57" s="19" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="30" t="inlineStr">
-        <is>
-          <t>其它</t>
-        </is>
-      </c>
-      <c r="B58" s="31" t="inlineStr">
-        <is>
-          <t>香菇</t>
-        </is>
-      </c>
-      <c r="C58" s="32" t="n">
-        <v>50</v>
-      </c>
-      <c r="D58" s="33" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E58" s="30" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="26" t="inlineStr">
+        <is>
+          <t>肉禽蛋</t>
+        </is>
+      </c>
+      <c r="B57" s="27" t="inlineStr">
+        <is>
+          <t>鸭蛋</t>
+        </is>
+      </c>
+      <c r="C57" s="28" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D57" s="36" t="inlineStr">
+        <is>
+          <t>↑ +1.56%</t>
+        </is>
+      </c>
+      <c r="E57" s="26" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
       </c>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="25" t="inlineStr">
+        <is>
+          <t>📂 水产（6 个品种）</t>
+        </is>
+      </c>
+      <c r="B58" s="19" t="n"/>
+      <c r="C58" s="19" t="n"/>
+      <c r="D58" s="19" t="n"/>
+      <c r="E58" s="19" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="26" t="inlineStr">
         <is>
-          <t>其它</t>
+          <t>水产</t>
         </is>
       </c>
       <c r="B59" s="27" t="inlineStr">
         <is>
-          <t>水豆腐（块）</t>
+          <t>冻带鱼（250g）</t>
         </is>
       </c>
       <c r="C59" s="28" t="n">
-        <v>2</v>
+        <v>22.5</v>
       </c>
       <c r="D59" s="29" t="inlineStr">
         <is>
@@ -4423,16 +4437,16 @@
     <row r="60">
       <c r="A60" s="30" t="inlineStr">
         <is>
-          <t>其它</t>
+          <t>水产</t>
         </is>
       </c>
       <c r="B60" s="31" t="inlineStr">
         <is>
-          <t>晶华自然盐（400g/袋）</t>
+          <t>草鱼（1000g）</t>
         </is>
       </c>
       <c r="C60" s="32" t="n">
-        <v>2</v>
+        <v>10.5</v>
       </c>
       <c r="D60" s="33" t="inlineStr">
         <is>
@@ -4448,16 +4462,16 @@
     <row r="61">
       <c r="A61" s="26" t="inlineStr">
         <is>
-          <t>其它</t>
+          <t>水产</t>
         </is>
       </c>
       <c r="B61" s="27" t="inlineStr">
         <is>
-          <t>冰度白砂糖（400g/袋）</t>
+          <t>冻黄鱼（500g）</t>
         </is>
       </c>
       <c r="C61" s="28" t="n">
-        <v>4.9</v>
+        <v>26</v>
       </c>
       <c r="D61" s="29" t="inlineStr">
         <is>
@@ -4473,16 +4487,16 @@
     <row r="62">
       <c r="A62" s="30" t="inlineStr">
         <is>
-          <t>其它</t>
+          <t>水产</t>
         </is>
       </c>
       <c r="B62" s="31" t="inlineStr">
         <is>
-          <t>冰度红糖（400g/袋）</t>
+          <t>鳙鱼（1500g）</t>
         </is>
       </c>
       <c r="C62" s="32" t="n">
-        <v>5.4</v>
+        <v>13</v>
       </c>
       <c r="D62" s="33" t="inlineStr">
         <is>
@@ -4498,16 +4512,16 @@
     <row r="63">
       <c r="A63" s="26" t="inlineStr">
         <is>
-          <t>其它</t>
+          <t>水产</t>
         </is>
       </c>
       <c r="B63" s="27" t="inlineStr">
         <is>
-          <t>恒顺陈醋（500ml/瓶）</t>
+          <t>白鲫鱼（350g）</t>
         </is>
       </c>
       <c r="C63" s="28" t="n">
-        <v>6.6</v>
+        <v>13.75</v>
       </c>
       <c r="D63" s="29" t="inlineStr">
         <is>
@@ -4523,53 +4537,851 @@
     <row r="64">
       <c r="A64" s="30" t="inlineStr">
         <is>
+          <t>水产</t>
+        </is>
+      </c>
+      <c r="B64" s="31" t="inlineStr">
+        <is>
+          <t>活虾（10cm）</t>
+        </is>
+      </c>
+      <c r="C64" s="32" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="D64" s="34" t="inlineStr">
+        <is>
+          <t>↑ +0.70%</t>
+        </is>
+      </c>
+      <c r="E64" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" s="25" t="inlineStr">
+        <is>
+          <t>📂 粮油（24 个品种）</t>
+        </is>
+      </c>
+      <c r="B65" s="19" t="n"/>
+      <c r="C65" s="19" t="n"/>
+      <c r="D65" s="19" t="n"/>
+      <c r="E65" s="19" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="30" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B66" s="31" t="inlineStr">
+        <is>
+          <t>黄豆</t>
+        </is>
+      </c>
+      <c r="C66" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D66" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E66" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="26" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B67" s="27" t="inlineStr">
+        <is>
+          <t>绿豆</t>
+        </is>
+      </c>
+      <c r="C67" s="28" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="D67" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E67" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B68" s="31" t="inlineStr">
+        <is>
+          <t>晚籼米（煮干饭）</t>
+        </is>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D68" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="26" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B69" s="27" t="inlineStr">
+        <is>
+          <t>粳米（珍珠米煮稀饭）</t>
+        </is>
+      </c>
+      <c r="C69" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D69" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E69" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="inlineStr">
+        <is>
+          <t>东北米（珍珠米）5公斤小包装</t>
+        </is>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="D70" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E70" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="26" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B71" s="27" t="inlineStr">
+        <is>
+          <t>面粉（标准粉）</t>
+        </is>
+      </c>
+      <c r="C71" s="28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D71" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E71" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="30" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B72" s="31" t="inlineStr">
+        <is>
+          <t>菜籽油（5L/桶）金龙鱼</t>
+        </is>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>70</v>
+      </c>
+      <c r="D72" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E72" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="26" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B73" s="27" t="inlineStr">
+        <is>
+          <t>大豆油（5L/桶）金龙鱼</t>
+        </is>
+      </c>
+      <c r="C73" s="28" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="D73" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E73" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="30" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="inlineStr">
+        <is>
+          <t>花生油（5L/桶）金龙鱼</t>
+        </is>
+      </c>
+      <c r="C74" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="D74" s="35" t="inlineStr">
+        <is>
+          <t>↓ -1.64%</t>
+        </is>
+      </c>
+      <c r="E74" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="26" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B75" s="27" t="inlineStr">
+        <is>
+          <t>第二代食用调和油（5L/桶）金龙鱼</t>
+        </is>
+      </c>
+      <c r="C75" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="D75" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E75" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B76" s="31" t="inlineStr">
+        <is>
+          <t>鲁花花生油（5L/桶）</t>
+        </is>
+      </c>
+      <c r="C76" s="32" t="n">
+        <v>150</v>
+      </c>
+      <c r="D76" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="26" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B77" s="27" t="inlineStr">
+        <is>
+          <t>金鼠香米（斤）</t>
+        </is>
+      </c>
+      <c r="C77" s="28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D77" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E77" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B78" s="31" t="inlineStr">
+        <is>
+          <t>广洋湖香粘米（斤）</t>
+        </is>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D78" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E78" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="26" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B79" s="27" t="inlineStr">
+        <is>
+          <t>盘锦大米（斤）</t>
+        </is>
+      </c>
+      <c r="C79" s="28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D79" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E79" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="30" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B80" s="31" t="inlineStr">
+        <is>
+          <t>洪家鸡油粘香米（5KG/包）</t>
+        </is>
+      </c>
+      <c r="C80" s="32" t="n">
+        <v>39</v>
+      </c>
+      <c r="D80" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E80" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="26" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B81" s="27" t="inlineStr">
+        <is>
+          <t>十月稻田长粒香米（5KG/包）</t>
+        </is>
+      </c>
+      <c r="C81" s="28" t="n">
+        <v>70</v>
+      </c>
+      <c r="D81" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E81" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="30" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B82" s="31" t="inlineStr">
+        <is>
+          <t>十月稻田香稻贡米（5KG/包）</t>
+        </is>
+      </c>
+      <c r="C82" s="32" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="D82" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E82" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="26" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B83" s="27" t="inlineStr">
+        <is>
+          <t>小悦米（5KG/包）</t>
+        </is>
+      </c>
+      <c r="C83" s="28" t="n">
+        <v>48</v>
+      </c>
+      <c r="D83" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E83" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="30" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B84" s="31" t="inlineStr">
+        <is>
+          <t>九三非转基因大豆油（10L/桶）</t>
+        </is>
+      </c>
+      <c r="C84" s="32" t="n">
+        <v>160</v>
+      </c>
+      <c r="D84" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E84" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="26" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B85" s="27" t="inlineStr">
+        <is>
+          <t>九三压榨浓香花生油（5L/桶）</t>
+        </is>
+      </c>
+      <c r="C85" s="28" t="n">
+        <v>158</v>
+      </c>
+      <c r="D85" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E85" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="30" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B86" s="31" t="inlineStr">
+        <is>
+          <t>馒头粉（斤）</t>
+        </is>
+      </c>
+      <c r="C86" s="32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D86" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E86" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="26" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B87" s="27" t="inlineStr">
+        <is>
+          <t>玉米淀粉（斤）</t>
+        </is>
+      </c>
+      <c r="C87" s="28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D87" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E87" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="30" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B88" s="31" t="inlineStr">
+        <is>
+          <t>大树碱面（1500g/件）</t>
+        </is>
+      </c>
+      <c r="C88" s="32" t="n">
+        <v>41</v>
+      </c>
+      <c r="D88" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E88" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="26" t="inlineStr">
+        <is>
+          <t>粮油</t>
+        </is>
+      </c>
+      <c r="B89" s="27" t="inlineStr">
+        <is>
+          <t>糯米</t>
+        </is>
+      </c>
+      <c r="C89" s="28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D89" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E89" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="24" customHeight="1">
+      <c r="A90" s="25" t="inlineStr">
+        <is>
+          <t>📂 其它（7 个品种）</t>
+        </is>
+      </c>
+      <c r="B90" s="19" t="n"/>
+      <c r="C90" s="19" t="n"/>
+      <c r="D90" s="19" t="n"/>
+      <c r="E90" s="19" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="26" t="inlineStr">
+        <is>
           <t>其它</t>
         </is>
       </c>
-      <c r="B64" s="31" t="inlineStr">
+      <c r="B91" s="27" t="inlineStr">
+        <is>
+          <t>香菇</t>
+        </is>
+      </c>
+      <c r="C91" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="D91" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E91" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="30" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="B92" s="31" t="inlineStr">
+        <is>
+          <t>水豆腐（块）</t>
+        </is>
+      </c>
+      <c r="C92" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D92" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E92" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="26" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="B93" s="27" t="inlineStr">
+        <is>
+          <t>晶华自然盐（400g/袋）</t>
+        </is>
+      </c>
+      <c r="C93" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D93" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E93" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="30" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="B94" s="31" t="inlineStr">
+        <is>
+          <t>冰度白砂糖（400g/袋）</t>
+        </is>
+      </c>
+      <c r="C94" s="32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D94" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E94" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="26" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="B95" s="27" t="inlineStr">
+        <is>
+          <t>冰度红糖（400g/袋）</t>
+        </is>
+      </c>
+      <c r="C95" s="28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D95" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E95" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="30" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="B96" s="31" t="inlineStr">
+        <is>
+          <t>恒顺陈醋（500ml/瓶）</t>
+        </is>
+      </c>
+      <c r="C96" s="32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D96" s="33" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E96" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="26" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="B97" s="27" t="inlineStr">
         <is>
           <t>蜜蜂味精（454g/袋）</t>
         </is>
       </c>
-      <c r="C64" s="32" t="n">
+      <c r="C97" s="28" t="n">
         <v>8</v>
       </c>
-      <c r="D64" s="33" t="inlineStr">
-        <is>
-          <t>→ 0.00%</t>
-        </is>
-      </c>
-      <c r="E64" s="30" t="inlineStr">
+      <c r="D97" s="29" t="inlineStr">
+        <is>
+          <t>→ 0.00%</t>
+        </is>
+      </c>
+      <c r="E97" s="26" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="38" t="inlineStr">
-        <is>
-          <t>📊 共 56 个品种 | 上涨 3 | 下跌 4 | 持平 49 | 无对比 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="39" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="38" t="inlineStr">
+        <is>
+          <t>📊 共 88 个品种 | 上涨 9 | 下跌 5 | 持平 65 | 无对比 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="39" t="inlineStr">
         <is>
           <t>↑ 红色=涨  ↓ 绿色=跌  → 灰色=持平  — =无上日数据</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A100:E100"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A47:E47"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A58:E58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
